--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -560,25 +560,25 @@
         <v>2026</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3233</v>
+        <v>1091288</v>
       </c>
       <c r="D2" t="n">
-        <v>1402</v>
+        <v>477326</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="F2" t="n">
-        <v>310</v>
+        <v>158083</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1808</v>
       </c>
       <c r="H2" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -626,10 +626,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>9070</v>
+        <v>645014</v>
       </c>
       <c r="Y2" t="n">
-        <v>-5837</v>
+        <v>446274</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,83 +553,6 @@
         <is>
           <t>淨利</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1091288</v>
-      </c>
-      <c r="D2" t="n">
-        <v>477326</v>
-      </c>
-      <c r="E2" t="n">
-        <v>559</v>
-      </c>
-      <c r="F2" t="n">
-        <v>158083</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1808</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1231</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1900</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4107</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>645014</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>446274</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,6 +553,83 @@
         <is>
           <t>淨利</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1091288</v>
+      </c>
+      <c r="D2" t="n">
+        <v>477326</v>
+      </c>
+      <c r="E2" t="n">
+        <v>559</v>
+      </c>
+      <c r="F2" t="n">
+        <v>158083</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1808</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-260</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1231</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1900</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4107</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>644754</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>446534</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -593,7 +593,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -623,13 +623,13 @@
         <v>4107</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="X2" t="n">
-        <v>644754</v>
+        <v>694754</v>
       </c>
       <c r="Y2" t="n">
-        <v>446534</v>
+        <v>396534</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -626,10 +626,10 @@
         <v>50000</v>
       </c>
       <c r="X2" t="n">
-        <v>694754</v>
+        <v>694759</v>
       </c>
       <c r="Y2" t="n">
-        <v>396534</v>
+        <v>396529</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -626,10 +626,10 @@
         <v>50000</v>
       </c>
       <c r="X2" t="n">
-        <v>694759</v>
+        <v>694754</v>
       </c>
       <c r="Y2" t="n">
-        <v>396529</v>
+        <v>396534</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,28 +557,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>1091288</v>
+        <v>1095164</v>
       </c>
       <c r="D2" t="n">
-        <v>477326</v>
+        <v>488993</v>
       </c>
       <c r="E2" t="n">
-        <v>559</v>
+        <v>34394</v>
       </c>
       <c r="F2" t="n">
-        <v>158083</v>
+        <v>154484</v>
       </c>
       <c r="G2" t="n">
-        <v>1808</v>
+        <v>1635</v>
       </c>
       <c r="H2" t="n">
-        <v>-260</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -623,13 +623,167 @@
         <v>4107</v>
       </c>
       <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>686744</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>408420</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1091288</v>
+      </c>
+      <c r="D3" t="n">
+        <v>477326</v>
+      </c>
+      <c r="E3" t="n">
+        <v>16005</v>
+      </c>
+      <c r="F3" t="n">
+        <v>158083</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1808</v>
+      </c>
+      <c r="H3" t="n">
+        <v>260</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>50000</v>
       </c>
-      <c r="X2" t="n">
-        <v>694754</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>396534</v>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1231</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1900</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4107</v>
+      </c>
+      <c r="W3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>710720</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>380568</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>357041</v>
+      </c>
+      <c r="D4" t="n">
+        <v>145786</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6737</v>
+      </c>
+      <c r="F4" t="n">
+        <v>51639</v>
+      </c>
+      <c r="G4" t="n">
+        <v>855</v>
+      </c>
+      <c r="H4" t="n">
+        <v>90</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1231</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1900</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4107</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>212345</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>144696</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,28 +557,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1095164</v>
+        <v>1091288</v>
       </c>
       <c r="D2" t="n">
-        <v>488993</v>
+        <v>477326</v>
       </c>
       <c r="E2" t="n">
-        <v>34394</v>
+        <v>16005</v>
       </c>
       <c r="F2" t="n">
-        <v>154484</v>
+        <v>158083</v>
       </c>
       <c r="G2" t="n">
-        <v>1635</v>
+        <v>1808</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -623,167 +623,13 @@
         <v>4107</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="X2" t="n">
-        <v>686744</v>
+        <v>710720</v>
       </c>
       <c r="Y2" t="n">
-        <v>408420</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1091288</v>
-      </c>
-      <c r="D3" t="n">
-        <v>477326</v>
-      </c>
-      <c r="E3" t="n">
-        <v>16005</v>
-      </c>
-      <c r="F3" t="n">
-        <v>158083</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1808</v>
-      </c>
-      <c r="H3" t="n">
-        <v>260</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1231</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1900</v>
-      </c>
-      <c r="V3" t="n">
-        <v>4107</v>
-      </c>
-      <c r="W3" t="n">
-        <v>50000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>710720</v>
-      </c>
-      <c r="Y3" t="n">
         <v>380568</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>357041</v>
-      </c>
-      <c r="D4" t="n">
-        <v>145786</v>
-      </c>
-      <c r="E4" t="n">
-        <v>6737</v>
-      </c>
-      <c r="F4" t="n">
-        <v>51639</v>
-      </c>
-      <c r="G4" t="n">
-        <v>855</v>
-      </c>
-      <c r="H4" t="n">
-        <v>90</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1231</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1900</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4107</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>212345</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>144696</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,83 +553,6 @@
         <is>
           <t>淨利</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1091288</v>
-      </c>
-      <c r="D2" t="n">
-        <v>477326</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16005</v>
-      </c>
-      <c r="F2" t="n">
-        <v>158083</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1808</v>
-      </c>
-      <c r="H2" t="n">
-        <v>260</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>50000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1231</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1900</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4107</v>
-      </c>
-      <c r="W2" t="n">
-        <v>50000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>710720</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>380568</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,6 +553,160 @@
         <is>
           <t>淨利</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1095164</v>
+      </c>
+      <c r="D2" t="n">
+        <v>489763</v>
+      </c>
+      <c r="E2" t="n">
+        <v>35599</v>
+      </c>
+      <c r="F2" t="n">
+        <v>154484</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1635</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1231</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1900</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4107</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>688719</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>406445</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>357041</v>
+      </c>
+      <c r="D3" t="n">
+        <v>146907</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6737</v>
+      </c>
+      <c r="F3" t="n">
+        <v>51639</v>
+      </c>
+      <c r="G3" t="n">
+        <v>855</v>
+      </c>
+      <c r="H3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1231</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1900</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4107</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>213466</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>143575</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y3"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,160 +553,6 @@
         <is>
           <t>淨利</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1095164</v>
-      </c>
-      <c r="D2" t="n">
-        <v>489763</v>
-      </c>
-      <c r="E2" t="n">
-        <v>35599</v>
-      </c>
-      <c r="F2" t="n">
-        <v>154484</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1635</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1231</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1900</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4107</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>688719</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>406445</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>357041</v>
-      </c>
-      <c r="D3" t="n">
-        <v>146907</v>
-      </c>
-      <c r="E3" t="n">
-        <v>6737</v>
-      </c>
-      <c r="F3" t="n">
-        <v>51639</v>
-      </c>
-      <c r="G3" t="n">
-        <v>855</v>
-      </c>
-      <c r="H3" t="n">
-        <v>90</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1231</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1900</v>
-      </c>
-      <c r="V3" t="n">
-        <v>4107</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>213466</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>143575</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,6 +553,83 @@
         <is>
           <t>淨利</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1091288</v>
+      </c>
+      <c r="D2" t="n">
+        <v>477085</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16005</v>
+      </c>
+      <c r="F2" t="n">
+        <v>158083</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1808</v>
+      </c>
+      <c r="H2" t="n">
+        <v>260</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1231</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1900</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4107</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>660479</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>430809</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -581,37 +581,37 @@
         <v>260</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
         <v>1231</v>
@@ -623,13 +623,13 @@
         <v>4107</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="X2" t="n">
-        <v>660479</v>
+        <v>660589</v>
       </c>
       <c r="Y2" t="n">
-        <v>430809</v>
+        <v>430699</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -617,7 +617,7 @@
         <v>1231</v>
       </c>
       <c r="U2" t="n">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="V2" t="n">
         <v>4107</v>
@@ -626,10 +626,10 @@
         <v>50</v>
       </c>
       <c r="X2" t="n">
-        <v>660589</v>
+        <v>660689</v>
       </c>
       <c r="Y2" t="n">
-        <v>430699</v>
+        <v>430599</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -614,7 +614,7 @@
         <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>1231</v>
+        <v>5000</v>
       </c>
       <c r="U2" t="n">
         <v>2000</v>
@@ -626,10 +626,10 @@
         <v>50</v>
       </c>
       <c r="X2" t="n">
-        <v>660689</v>
+        <v>664458</v>
       </c>
       <c r="Y2" t="n">
-        <v>430599</v>
+        <v>426830</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,83 +553,6 @@
         <is>
           <t>淨利</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1091288</v>
-      </c>
-      <c r="D2" t="n">
-        <v>477085</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16005</v>
-      </c>
-      <c r="F2" t="n">
-        <v>158083</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1808</v>
-      </c>
-      <c r="H2" t="n">
-        <v>260</v>
-      </c>
-      <c r="I2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K2" t="n">
-        <v>10</v>
-      </c>
-      <c r="L2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N2" t="n">
-        <v>10</v>
-      </c>
-      <c r="O2" t="n">
-        <v>10</v>
-      </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>10</v>
-      </c>
-      <c r="R2" t="n">
-        <v>10</v>
-      </c>
-      <c r="S2" t="n">
-        <v>10</v>
-      </c>
-      <c r="T2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4107</v>
-      </c>
-      <c r="W2" t="n">
-        <v>50</v>
-      </c>
-      <c r="X2" t="n">
-        <v>664458</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>426830</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,211 +413,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>年份</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>月份</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>營業額</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>商品成本</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>折扣優惠</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>手續費</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>未取貨/退貨運費</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>物流處理費（運費差額）</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>其他費用（一）</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>其他費用（二）</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>薪資費用</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>委製費用</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>蝦皮廣告費用</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>露天廣告費用</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>MO店廣告費用</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>官網廣告費用</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>其他廣告費用</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>耗材費用</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>營業稅額</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>官網月費</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>會計記帳費</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>會費＆勞健保費</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>廣告費用合計</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>總成本</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>淨利</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1091288</v>
-      </c>
-      <c r="D2" t="n">
-        <v>477085</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16005</v>
-      </c>
-      <c r="F2" t="n">
-        <v>158083</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1808</v>
-      </c>
-      <c r="H2" t="n">
-        <v>260</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1231</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1900</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4107</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>660479</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>430809</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,6 +541,83 @@
         <is>
           <t>淨利</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1091288</v>
+      </c>
+      <c r="D2" t="n">
+        <v>477085</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16005</v>
+      </c>
+      <c r="F2" t="n">
+        <v>158083</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1808</v>
+      </c>
+      <c r="H2" t="n">
+        <v>260</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1231</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1900</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4107</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>660479</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>430809</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>8265</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -614,10 +614,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>660479</v>
+        <v>668744</v>
       </c>
       <c r="Y2" t="n">
-        <v>430809</v>
+        <v>422544</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -587,7 +587,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -611,13 +611,13 @@
         <v>4107</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X2" t="n">
-        <v>668744</v>
+        <v>673744</v>
       </c>
       <c r="Y2" t="n">
-        <v>422544</v>
+        <v>417544</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -569,7 +569,7 @@
         <v>260</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -614,10 +614,10 @@
         <v>5000</v>
       </c>
       <c r="X2" t="n">
-        <v>673744</v>
+        <v>680744</v>
       </c>
       <c r="Y2" t="n">
-        <v>417544</v>
+        <v>410544</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -581,7 +581,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>144651</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -611,13 +611,13 @@
         <v>4107</v>
       </c>
       <c r="W2" t="n">
-        <v>5000</v>
+        <v>149651</v>
       </c>
       <c r="X2" t="n">
-        <v>680744</v>
+        <v>825395</v>
       </c>
       <c r="Y2" t="n">
-        <v>410544</v>
+        <v>265893</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>48729</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -614,10 +614,10 @@
         <v>149651</v>
       </c>
       <c r="X2" t="n">
-        <v>825395</v>
+        <v>874124</v>
       </c>
       <c r="Y2" t="n">
-        <v>265893</v>
+        <v>217164</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -578,7 +578,7 @@
         <v>48729</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3850</v>
       </c>
       <c r="M2" t="n">
         <v>144651</v>
@@ -614,10 +614,10 @@
         <v>149651</v>
       </c>
       <c r="X2" t="n">
-        <v>874124</v>
+        <v>877974</v>
       </c>
       <c r="Y2" t="n">
-        <v>217164</v>
+        <v>213314</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -578,7 +578,7 @@
         <v>48729</v>
       </c>
       <c r="L2" t="n">
-        <v>3850</v>
+        <v>4950</v>
       </c>
       <c r="M2" t="n">
         <v>144651</v>
@@ -614,10 +614,10 @@
         <v>149651</v>
       </c>
       <c r="X2" t="n">
-        <v>877974</v>
+        <v>879074</v>
       </c>
       <c r="Y2" t="n">
-        <v>213314</v>
+        <v>212214</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,83 +541,6 @@
         <is>
           <t>淨利</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1091288</v>
-      </c>
-      <c r="D2" t="n">
-        <v>477085</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16005</v>
-      </c>
-      <c r="F2" t="n">
-        <v>158083</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1808</v>
-      </c>
-      <c r="H2" t="n">
-        <v>260</v>
-      </c>
-      <c r="I2" t="n">
-        <v>7000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>48729</v>
-      </c>
-      <c r="L2" t="n">
-        <v>4950</v>
-      </c>
-      <c r="M2" t="n">
-        <v>144651</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>8265</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1231</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1900</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4107</v>
-      </c>
-      <c r="W2" t="n">
-        <v>149651</v>
-      </c>
-      <c r="X2" t="n">
-        <v>879074</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>212214</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -413,19 +413,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DiscountPolicy</t>
+          <t>年份</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>MonthKey</t>
-        </is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>營業額</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>商品成本</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>折扣優惠</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>手續費</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>未取貨/退貨運費</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>物流處理費（運費差額）</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>其他費用（一）</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>其他費用（二）</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>薪資費用</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>委製費用</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>蝦皮廣告費用</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>露天廣告費用</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>MO店廣告費用</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>官網廣告費用</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>其他廣告費用</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>耗材費用</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>營業稅額</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>官網月費</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>會計記帳費</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>會費＆勞健保費</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>廣告費用合計</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>總成本</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>淨利</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1091288</v>
+      </c>
+      <c r="D2" t="n">
+        <v>477085</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16005</v>
+      </c>
+      <c r="F2" t="n">
+        <v>158083</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1808</v>
+      </c>
+      <c r="H2" t="n">
+        <v>260</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>48729</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4950</v>
+      </c>
+      <c r="M2" t="n">
+        <v>144651</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>8265</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1231</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1900</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4107</v>
+      </c>
+      <c r="W2" t="n">
+        <v>149651</v>
+      </c>
+      <c r="X2" t="n">
+        <v>879074</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>212214</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -569,25 +569,25 @@
         <v>260</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>48729</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4950</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>144651</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>8265</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -611,13 +611,13 @@
         <v>4107</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>149651</v>
       </c>
       <c r="X2" t="n">
-        <v>660479</v>
+        <v>879074</v>
       </c>
       <c r="Y2" t="n">
-        <v>430809</v>
+        <v>212214</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,6 +618,83 @@
       </c>
       <c r="Y2" t="n">
         <v>212214</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>778267</v>
+      </c>
+      <c r="D3" t="n">
+        <v>349565</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14609</v>
+      </c>
+      <c r="F3" t="n">
+        <v>112560</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1620</v>
+      </c>
+      <c r="H3" t="n">
+        <v>115</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1231</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1900</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4107</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>485707</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>292560</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>105716</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -688,13 +688,13 @@
         <v>4107</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>105716</v>
       </c>
       <c r="X3" t="n">
-        <v>485707</v>
+        <v>591423</v>
       </c>
       <c r="Y3" t="n">
-        <v>292560</v>
+        <v>186844</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>105716</v>
+        <v>115670</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -688,13 +688,13 @@
         <v>4107</v>
       </c>
       <c r="W3" t="n">
-        <v>105716</v>
+        <v>115670</v>
       </c>
       <c r="X3" t="n">
-        <v>591423</v>
+        <v>601377</v>
       </c>
       <c r="Y3" t="n">
-        <v>186844</v>
+        <v>176890</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2407</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -691,10 +691,10 @@
         <v>115670</v>
       </c>
       <c r="X3" t="n">
-        <v>601377</v>
+        <v>603784</v>
       </c>
       <c r="Y3" t="n">
-        <v>176890</v>
+        <v>174483</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -599,7 +599,7 @@
         <v>8265</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>26406</v>
       </c>
       <c r="T2" t="n">
         <v>1231</v>
@@ -614,10 +614,10 @@
         <v>149651</v>
       </c>
       <c r="X2" t="n">
-        <v>879074</v>
+        <v>905480</v>
       </c>
       <c r="Y2" t="n">
-        <v>212214</v>
+        <v>185808</v>
       </c>
     </row>
     <row r="3">
@@ -652,10 +652,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>29763</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="M3" t="n">
         <v>115670</v>
@@ -691,10 +691,10 @@
         <v>115670</v>
       </c>
       <c r="X3" t="n">
-        <v>603784</v>
+        <v>634947</v>
       </c>
       <c r="Y3" t="n">
-        <v>174483</v>
+        <v>143320</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -676,7 +676,7 @@
         <v>2407</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>18753</v>
       </c>
       <c r="T3" t="n">
         <v>1231</v>
@@ -691,10 +691,10 @@
         <v>115670</v>
       </c>
       <c r="X3" t="n">
-        <v>634947</v>
+        <v>653700</v>
       </c>
       <c r="Y3" t="n">
-        <v>143320</v>
+        <v>124567</v>
       </c>
     </row>
   </sheetData>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -576,7 +576,7 @@
         <v>1128090</v>
       </c>
       <c r="D2" t="n">
-        <v>520046</v>
+        <v>520782</v>
       </c>
       <c r="E2" t="n">
         <v>53250</v>
@@ -639,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>740412</v>
+        <v>741148</v>
       </c>
       <c r="Z2" t="n">
-        <v>387678</v>
+        <v>386942</v>
       </c>
       <c r="AA2" t="inlineStr"/>
     </row>
@@ -750,7 +750,7 @@
         <v>465</v>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -801,10 +801,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>465910</v>
+        <v>465948</v>
       </c>
       <c r="Z4" t="n">
-        <v>218671</v>
+        <v>218633</v>
       </c>
       <c r="AA4" t="inlineStr"/>
     </row>
@@ -900,7 +900,7 @@
         <v>936228</v>
       </c>
       <c r="D6" t="n">
-        <v>461558</v>
+        <v>461572</v>
       </c>
       <c r="E6" t="n">
         <v>27864</v>
@@ -909,10 +909,10 @@
         <v>131914</v>
       </c>
       <c r="G6" t="n">
-        <v>935</v>
+        <v>973</v>
       </c>
       <c r="H6" t="n">
-        <v>80</v>
+        <v>238</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>630744</v>
+        <v>630954</v>
       </c>
       <c r="Z6" t="n">
-        <v>305484</v>
+        <v>305274</v>
       </c>
       <c r="AA6" t="inlineStr"/>
     </row>
@@ -993,7 +993,7 @@
         <v>1580</v>
       </c>
       <c r="H7" t="n">
-        <v>-15</v>
+        <v>45</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1044,10 +1044,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>928356</v>
+        <v>928416</v>
       </c>
       <c r="Z7" t="n">
-        <v>453440</v>
+        <v>453380</v>
       </c>
       <c r="AA7" t="inlineStr"/>
     </row>
@@ -1059,10 +1059,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>1190413</v>
+        <v>1190216</v>
       </c>
       <c r="D8" t="n">
-        <v>580618</v>
+        <v>580522</v>
       </c>
       <c r="E8" t="n">
         <v>42116</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>799692</v>
+        <v>799596</v>
       </c>
       <c r="Z8" t="n">
-        <v>390721</v>
+        <v>390620</v>
       </c>
       <c r="AA8" t="inlineStr"/>
     </row>
@@ -1305,7 +1305,7 @@
         <v>720377</v>
       </c>
       <c r="D11" t="n">
-        <v>347696</v>
+        <v>347706</v>
       </c>
       <c r="E11" t="n">
         <v>34931</v>
@@ -1317,7 +1317,7 @@
         <v>450</v>
       </c>
       <c r="H11" t="n">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1368,10 +1368,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>490778</v>
+        <v>490848</v>
       </c>
       <c r="Z11" t="n">
-        <v>229599</v>
+        <v>229529</v>
       </c>
       <c r="AA11" t="inlineStr"/>
     </row>
@@ -1386,7 +1386,7 @@
         <v>1109036</v>
       </c>
       <c r="D12" t="n">
-        <v>518014</v>
+        <v>518034</v>
       </c>
       <c r="E12" t="n">
         <v>55804</v>
@@ -1398,7 +1398,7 @@
         <v>1245</v>
       </c>
       <c r="H12" t="n">
-        <v>85</v>
+        <v>183</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1449,10 +1449,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>736873</v>
+        <v>736991</v>
       </c>
       <c r="Z12" t="n">
-        <v>372163</v>
+        <v>372045</v>
       </c>
       <c r="AA12" t="inlineStr"/>
     </row>
@@ -1479,7 +1479,7 @@
         <v>1555</v>
       </c>
       <c r="H13" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1530,10 +1530,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>694099</v>
+        <v>694159</v>
       </c>
       <c r="Z13" t="n">
-        <v>403879</v>
+        <v>403819</v>
       </c>
       <c r="AA13" t="inlineStr"/>
     </row>

--- a/data/月報表.xlsx
+++ b/data/月報表.xlsx
@@ -597,16 +597,20 @@
         <v>1260</v>
       </c>
       <c r="K2" t="n">
-        <v>28523</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>28522</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
       <c r="M2" t="n">
-        <v>97348.992</v>
+        <v>97348</v>
       </c>
       <c r="N2" t="n">
         <v>800</v>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
@@ -617,7 +621,7 @@
         <v>30096</v>
       </c>
       <c r="S2" t="n">
-        <v>25104.25494368254</v>
+        <v>25104</v>
       </c>
       <c r="T2" t="n">
         <v>1231</v>
@@ -632,13 +636,13 @@
         <v>1155</v>
       </c>
       <c r="X2" t="n">
-        <v>98149</v>
+        <v>98148</v>
       </c>
       <c r="Y2" t="n">
-        <v>929635</v>
+        <v>929633</v>
       </c>
       <c r="Z2" t="n">
-        <v>198455</v>
+        <v>198457</v>
       </c>
       <c r="AA2" t="inlineStr"/>
     </row>
@@ -676,14 +680,18 @@
       <c r="K3" t="n">
         <v>22367</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="M3" t="n">
-        <v>71034.292</v>
+        <v>71034</v>
       </c>
       <c r="N3" t="n">
         <v>800</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
@@ -694,7 +702,7 @@
         <v>3636</v>
       </c>
       <c r="S3" t="n">
-        <v>22348.74505631746</v>
+        <v>22348</v>
       </c>
       <c r="T3" t="n">
         <v>1231</v>
@@ -712,10 +720,10 @@
         <v>71834</v>
       </c>
       <c r="Y3" t="n">
-        <v>674839</v>
+        <v>674838</v>
       </c>
       <c r="Z3" t="n">
-        <v>151058</v>
+        <v>151059</v>
       </c>
       <c r="AA3" t="inlineStr"/>
     </row>
@@ -753,12 +761,18 @@
       <c r="K4" t="n">
         <v>24016</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="M4" t="n">
-        <v>72984.47600000001</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+        <v>72984</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
@@ -769,7 +783,7 @@
         <v>2123</v>
       </c>
       <c r="S4" t="n">
-        <v>10268.0495416443</v>
+        <v>10268</v>
       </c>
       <c r="T4" t="n">
         <v>1231</v>
@@ -787,10 +801,10 @@
         <v>72984</v>
       </c>
       <c r="Y4" t="n">
-        <v>578460</v>
+        <v>578459</v>
       </c>
       <c r="Z4" t="n">
-        <v>106121</v>
+        <v>106122</v>
       </c>
       <c r="AA4" t="inlineStr"/>
     </row>
@@ -820,7 +834,7 @@
         <v>240</v>
       </c>
       <c r="I5" t="n">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -828,12 +842,18 @@
       <c r="K5" t="n">
         <v>22045</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
       <c r="M5" t="n">
-        <v>79539.992</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>79539</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
@@ -844,7 +864,7 @@
         <v>2000</v>
       </c>
       <c r="S5" t="n">
-        <v>8780.950458355694</v>
+        <v>8780</v>
       </c>
       <c r="T5" t="n">
         <v>1231</v>
@@ -859,13 +879,13 @@
         <v>1155</v>
       </c>
       <c r="X5" t="n">
-        <v>79540</v>
+        <v>79539</v>
       </c>
       <c r="Y5" t="n">
-        <v>572065</v>
+        <v>572062</v>
       </c>
       <c r="Z5" t="n">
-        <v>86219</v>
+        <v>86222</v>
       </c>
       <c r="AA5" t="inlineStr"/>
     </row>
@@ -903,9 +923,11 @@
       <c r="K6" t="n">
         <v>21771</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
       <c r="M6" t="n">
-        <v>147119.74</v>
+        <v>147119</v>
       </c>
       <c r="N6" t="n">
         <v>1250</v>
@@ -923,7 +945,7 @@
         <v>4524</v>
       </c>
       <c r="S6" t="n">
-        <v>19452.19442616715</v>
+        <v>19452</v>
       </c>
       <c r="T6" t="n">
         <v>1231</v>
@@ -938,13 +960,13 @@
         <v>1155</v>
       </c>
       <c r="X6" t="n">
-        <v>156370</v>
+        <v>156369</v>
       </c>
       <c r="Y6" t="n">
-        <v>839044</v>
+        <v>839043</v>
       </c>
       <c r="Z6" t="n">
-        <v>97184</v>
+        <v>97185</v>
       </c>
       <c r="AA6" t="inlineStr"/>
     </row>
@@ -982,14 +1004,18 @@
       <c r="K7" t="n">
         <v>37820</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
       <c r="M7" t="n">
-        <v>238714.03</v>
+        <v>238714</v>
       </c>
       <c r="N7" t="n">
         <v>799</v>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
@@ -1000,7 +1026,7 @@
         <v>8207</v>
       </c>
       <c r="S7" t="n">
-        <v>28656.80557383285</v>
+        <v>28656</v>
       </c>
       <c r="T7" t="n">
         <v>1231</v>
@@ -1018,10 +1044,10 @@
         <v>239513</v>
       </c>
       <c r="Y7" t="n">
-        <v>1248293</v>
+        <v>1248292</v>
       </c>
       <c r="Z7" t="n">
-        <v>133503</v>
+        <v>133504</v>
       </c>
       <c r="AA7" t="inlineStr"/>
     </row>
@@ -1059,12 +1085,18 @@
       <c r="K8" t="n">
         <v>32763</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
       <c r="M8" t="n">
-        <v>217126.59</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+        <v>217126</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
@@ -1075,7 +1107,7 @@
         <v>3214</v>
       </c>
       <c r="S8" t="n">
-        <v>30074.1606939768</v>
+        <v>30074</v>
       </c>
       <c r="T8" t="n">
         <v>1231</v>
@@ -1090,13 +1122,13 @@
         <v>1155</v>
       </c>
       <c r="X8" t="n">
-        <v>217127</v>
+        <v>217126</v>
       </c>
       <c r="Y8" t="n">
-        <v>1089601</v>
+        <v>1089600</v>
       </c>
       <c r="Z8" t="n">
-        <v>100615</v>
+        <v>100616</v>
       </c>
       <c r="AA8" t="inlineStr"/>
     </row>
@@ -1138,10 +1170,14 @@
         <v>3240</v>
       </c>
       <c r="M9" t="n">
-        <v>157891.52</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+        <v>157891</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
@@ -1152,7 +1188,7 @@
         <v>3992</v>
       </c>
       <c r="S9" t="n">
-        <v>26144.8393060232</v>
+        <v>26144</v>
       </c>
       <c r="T9" t="n">
         <v>1231</v>
@@ -1167,13 +1203,13 @@
         <v>1155</v>
       </c>
       <c r="X9" t="n">
-        <v>157892</v>
+        <v>157891</v>
       </c>
       <c r="Y9" t="n">
-        <v>943106</v>
+        <v>943105</v>
       </c>
       <c r="Z9" t="n">
-        <v>104627</v>
+        <v>104628</v>
       </c>
       <c r="AA9" t="inlineStr"/>
     </row>
@@ -1211,12 +1247,18 @@
       <c r="K10" t="n">
         <v>26408</v>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="M10" t="n">
-        <v>109118.92</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+        <v>109118</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
@@ -1227,7 +1269,7 @@
         <v>1946</v>
       </c>
       <c r="S10" t="n">
-        <v>18711.5161044166</v>
+        <v>18711</v>
       </c>
       <c r="T10" t="n">
         <v>1231</v>
@@ -1242,13 +1284,13 @@
         <v>1155</v>
       </c>
       <c r="X10" t="n">
-        <v>109119</v>
+        <v>109118</v>
       </c>
       <c r="Y10" t="n">
-        <v>710516</v>
+        <v>710515</v>
       </c>
       <c r="Z10" t="n">
-        <v>95579</v>
+        <v>95580</v>
       </c>
       <c r="AA10" t="inlineStr"/>
     </row>
@@ -1278,7 +1320,7 @@
         <v>235</v>
       </c>
       <c r="I11" t="n">
-        <v>3713.606439064965</v>
+        <v>3713</v>
       </c>
       <c r="J11" t="n">
         <v>825</v>
@@ -1290,10 +1332,14 @@
         <v>3500</v>
       </c>
       <c r="M11" t="n">
-        <v>86552.01000000001</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+        <v>86552</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
@@ -1304,7 +1350,7 @@
         <v>5329</v>
       </c>
       <c r="S11" t="n">
-        <v>16306.48389558339</v>
+        <v>16306</v>
       </c>
       <c r="T11" t="n">
         <v>1231</v>
@@ -1322,10 +1368,10 @@
         <v>86552</v>
       </c>
       <c r="Y11" t="n">
-        <v>634060</v>
+        <v>634059</v>
       </c>
       <c r="Z11" t="n">
-        <v>86317</v>
+        <v>86318</v>
       </c>
       <c r="AA11" t="inlineStr"/>
     </row>
@@ -1367,9 +1413,11 @@
         <v>1750</v>
       </c>
       <c r="M12" t="n">
-        <v>181905.07</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>181905</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
       <c r="O12" t="n">
         <v>8000</v>
       </c>
@@ -1383,7 +1431,7 @@
         <v>17766</v>
       </c>
       <c r="S12" t="n">
-        <v>20330.64382658813</v>
+        <v>20330</v>
       </c>
       <c r="T12" t="n">
         <v>1231</v>
@@ -1401,10 +1449,10 @@
         <v>189905</v>
       </c>
       <c r="Y12" t="n">
-        <v>1018519</v>
+        <v>1018518</v>
       </c>
       <c r="Z12" t="n">
-        <v>90517</v>
+        <v>90518</v>
       </c>
       <c r="AA12" t="inlineStr"/>
     </row>
@@ -1446,7 +1494,7 @@
         <v>1350</v>
       </c>
       <c r="M13" t="n">
-        <v>157714.22</v>
+        <v>157714</v>
       </c>
       <c r="N13" t="n">
         <v>1600</v>
@@ -1464,7 +1512,7 @@
         <v>6180</v>
       </c>
       <c r="S13" t="n">
-        <v>21973.35617341187</v>
+        <v>21973</v>
       </c>
       <c r="T13" t="n">
         <v>1231</v>
@@ -1482,10 +1530,10 @@
         <v>170314</v>
       </c>
       <c r="Y13" t="n">
-        <v>947080</v>
+        <v>947079</v>
       </c>
       <c r="Z13" t="n">
-        <v>150898</v>
+        <v>150899</v>
       </c>
       <c r="AA13" t="inlineStr"/>
     </row>
